--- a/data/example/checkin/weight_loss/human_chat_history.xlsx
+++ b/data/example/checkin/weight_loss/human_chat_history.xlsx
@@ -474,14 +474,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>今天完成了25分钟快走和拉伸。</t>
+          <t>今天完成了22分钟快走和拉伸，晚餐控制得还可以。</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-02 19:07</t>
+          <t>2026-03-02 12:07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>@Ava #daily_activity_checkin 已记录，今天第1次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Ava #daily_activity_checkin 很棒，你最近执行得比较稳定。可以尝试把拉伸延长到8分钟，并注意控制晚餐主食比例。</t>
         </is>
       </c>
     </row>
@@ -540,14 +540,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>今天完成了30分钟快走和拉伸。</t>
+          <t>上午散步26分钟，晚上又补了力量训练，感觉状态不错。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-03 19:22</t>
+          <t>2026-03-03 13:22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>@Bella #daily_activity_checkin 已记录，今天第1次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Bella #daily_activity_checkin 这次反馈重点看步数和训练连续性。建议明天把步行安排在饭后，保持节奏，你在进步。</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>收到，谢谢老师，我明天继续打卡。</t>
+          <t>好的，我会按建议把饭后步行也加上。</t>
         </is>
       </c>
     </row>
@@ -606,14 +606,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>今天完成了35分钟快走和拉伸。</t>
+          <t>今天步数大概有6150步，还做了拉伸和深蹲。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-04 19:37</t>
+          <t>2026-03-04 11:37</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -628,14 +628,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>@Clara #daily_activity_checkin 已记录，今天第1次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Clara #daily_activity_checkin 今天的完成度不错。结合你目前的状态，推荐继续快走加简单抗阻训练，注意补水和睡眠。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-04 19:40</t>
+          <t>2026-03-04 14:40</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>@Clara #daily_activity_checkin 已记录，今天第2次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Clara #daily_activity_checkin 做得很好。根据你这周的记录，今天已经完成约35分钟活动，建议晚餐后再快走10分钟，继续保持步数。</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>收到，谢谢老师，我明天继续打卡。</t>
+          <t>明白了，我会继续保持今天的节奏。</t>
         </is>
       </c>
     </row>
@@ -694,14 +694,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>今天完成了40分钟快走和拉伸。</t>
+          <t>今天按照计划完成了有氧训练，运动后没有加餐。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-05 19:55</t>
+          <t>2026-03-05 12:55</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -716,14 +716,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>@Diana #daily_activity_checkin 已记录，今天第1次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Diana #daily_activity_checkin 做得很好。根据你这周的记录，今天已经完成约34分钟活动，建议晚餐后再快走10分钟，继续保持步数。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-05 19:58</t>
+          <t>2026-03-05 15:58</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>@Diana #daily_activity_checkin 已记录，今天第2次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Diana #daily_activity_checkin 很棒，你最近执行得比较稳定。可以尝试把拉伸延长到8分钟，并注意控制晚餐主食比例。</t>
         </is>
       </c>
     </row>
@@ -782,14 +782,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>今天完成了45分钟快走和拉伸。</t>
+          <t>今天完成了38分钟快走和拉伸，晚餐控制得还可以。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-06 19:13</t>
+          <t>2026-03-06 13:13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>@Elena #daily_activity_checkin 已记录，今天第1次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Elena #daily_activity_checkin 很棒，你最近执行得比较稳定。可以尝试把拉伸延长到8分钟，并注意控制晚餐主食比例。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-06 19:16</t>
+          <t>2026-03-06 16:16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>@Elena #daily_activity_checkin 已记录，今天第2次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Elena #daily_activity_checkin 这次反馈重点看步数和训练连续性。建议明天把步行安排在饭后，保持节奏，你在进步。</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>@Elena #daily_activity_checkin 已记录，今天第3次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Elena #daily_activity_checkin 今天的完成度不错。结合你目前的状态，推荐继续快走加简单抗阻训练，注意补水和睡眠。</t>
         </is>
       </c>
     </row>
@@ -870,7 +870,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>收到，谢谢老师，我明天继续打卡。</t>
+          <t>好的，我会按建议把饭后步行也加上。</t>
         </is>
       </c>
     </row>
@@ -892,14 +892,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>今天完成了50分钟快走和拉伸。</t>
+          <t>上午散步42分钟，晚上又补了力量训练，感觉状态不错。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-07 19:34</t>
+          <t>2026-03-07 11:34</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>@Fiona #daily_activity_checkin 已记录，今天第1次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Fiona #daily_activity_checkin 这次反馈重点看步数和训练连续性。建议明天把步行安排在饭后，保持节奏，你在进步。</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>收到，谢谢老师，我明天继续打卡。</t>
+          <t>明白了，我会继续保持今天的节奏。</t>
         </is>
       </c>
     </row>
@@ -958,14 +958,14 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>今天完成了55分钟快走和拉伸。</t>
+          <t>今天步数大概有8750步，还做了拉伸和深蹲。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-08 19:49</t>
+          <t>2026-03-08 12:49</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -980,14 +980,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>@Grace #daily_activity_checkin 已记录，今天第1次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Grace #daily_activity_checkin 今天的完成度不错。结合你目前的状态，推荐继续快走加简单抗阻训练，注意补水和睡眠。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-08 19:52</t>
+          <t>2026-03-08 15:52</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>@Grace #daily_activity_checkin 已记录，今天第2次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Grace #daily_activity_checkin 做得很好。根据你这周的记录，今天已经完成约51分钟活动，建议晚餐后再快走10分钟，继续保持步数。</t>
         </is>
       </c>
     </row>
@@ -1046,14 +1046,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>今天完成了60分钟快走和拉伸。</t>
+          <t>今天按照计划完成了有氧训练，运动后没有加餐。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-09 19:07</t>
+          <t>2026-03-09 13:07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1068,14 +1068,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>@Hazel #daily_activity_checkin 已记录，今天第1次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Hazel #daily_activity_checkin 做得很好。根据你这周的记录，今天已经完成约50分钟活动，建议晚餐后再快走10分钟，继续保持步数。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-09 19:10</t>
+          <t>2026-03-09 16:10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>@Hazel #daily_activity_checkin 已记录，今天第2次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Hazel #daily_activity_checkin 很棒，你最近执行得比较稳定。可以尝试把拉伸延长到8分钟，并注意控制晚餐主食比例。</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>@Hazel #daily_activity_checkin 已记录，今天第3次反馈：继续保持步数和晚餐控制。</t>
+          <t>@Hazel #daily_activity_checkin 这次反馈重点看步数和训练连续性。建议明天把步行安排在饭后，保持节奏，你在进步。</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>收到，谢谢老师，我明天继续打卡。</t>
+          <t>好的，我会按建议把饭后步行也加上。</t>
         </is>
       </c>
     </row>
